--- a/KPIs.xlsx
+++ b/KPIs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://batizci-my.sharepoint.com/personal/soporteoperativo_bci_mx/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EA120046-6275-46CF-9370-057DDB85D435}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DDAE7D5F-319B-4ABD-A579-2FE9C2B17F60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15780" xr2:uid="{D41C87DC-28A2-D24A-B6A7-3496D0695978}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15780" firstSheet="4" xr2:uid="{D41C87DC-28A2-D24A-B6A7-3496D0695978}"/>
   </bookViews>
   <sheets>
     <sheet name="Customer P1" sheetId="3" r:id="rId1"/>
@@ -191,12 +191,34 @@
         </r>
       </text>
     </comment>
+    <comment ref="J32" authorId="1" shapeId="0" xr:uid="{53F8A223-5793-4CD0-B821-F6941107EDF7}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color theme="1"/>
+            <rFont val="Aptos Narrow"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Daniela Baltierrez:
+2 REM: 1 mes  
+1 REM: 20 días 
+2 REM: 14 días 
+3 REM: 13 días 
+4 REM: 8 días 
+4 REM: 3 días 
+3 REM: 2 días 
+</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="202">
   <si>
     <t>Mes</t>
   </si>
@@ -408,6 +430,15 @@
     <t xml:space="preserve">Cargar en pre-factura remisiones </t>
   </si>
   <si>
+    <t xml:space="preserve">Correo obed revision material rechazo </t>
+  </si>
+  <si>
+    <t xml:space="preserve">revisar mercury rfq con yadira </t>
+  </si>
+  <si>
+    <t xml:space="preserve">embarque kimsu pend </t>
+  </si>
+  <si>
     <t xml:space="preserve">Cliente </t>
   </si>
   <si>
@@ -531,6 +562,15 @@
     <t>costo granalla envio de correo a hyster</t>
   </si>
   <si>
+    <t xml:space="preserve">kimsu cambio de costo y facturacion </t>
+  </si>
+  <si>
+    <t xml:space="preserve">heyang pedido cliente </t>
+  </si>
+  <si>
+    <t xml:space="preserve">programacion con edwin </t>
+  </si>
+  <si>
     <t>On Hand</t>
   </si>
   <si>
@@ -628,6 +668,9 @@
   </si>
   <si>
     <t xml:space="preserve">Envio de facturas,conteos de almacén, acomodo de estantes del almacén 2,pendientes de almacén de pintura,etiquetas de código de colores </t>
+  </si>
+  <si>
+    <t>Registro de facturas en bitacora,conteos diarios,LPA, acomodo de estantes de planta 2,almacén de pintura,etiquetas de código de colores</t>
   </si>
   <si>
     <t>Pendientes Cotización</t>
@@ -741,6 +784,15 @@
     <t>Placa a 1011. Cal 3/16 y Cal 10 (1)</t>
   </si>
   <si>
+    <t>Placa de 3/4 6x10 a572 G50 - 11-09-2026 (3)</t>
+  </si>
+  <si>
+    <t>CERTIFICADOS DE COLADA PLACA 1011 DE AYER</t>
+  </si>
+  <si>
+    <t>Reposicion Placa 3/4 desnivelada 29/09</t>
+  </si>
+  <si>
     <t>CLT-000001</t>
   </si>
   <si>
@@ -763,6 +815,9 @@
   </si>
   <si>
     <t>CLT-000138</t>
+  </si>
+  <si>
+    <t>CLT-000062</t>
   </si>
   <si>
     <t>SUBTOTAL</t>
@@ -791,15 +846,22 @@
   <si>
     <t>TECTRON METAL</t>
   </si>
+  <si>
+    <t>SEA SOLUCIONES</t>
+  </si>
+  <si>
+    <t>AGOSTO</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
     <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="14">
@@ -895,7 +957,7 @@
       <name val="Aptos Narrow"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -947,8 +1009,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="13">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -1100,6 +1168,19 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1109,7 +1190,7 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1239,7 +1320,6 @@
     <xf numFmtId="8" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1269,6 +1349,33 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -3445,11 +3552,11 @@
         <f>+Q27/P27</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="S27" s="54" t="s">
+      <c r="S27" s="53" t="s">
         <v>53</v>
       </c>
-      <c r="T27" s="55"/>
-      <c r="U27" s="56"/>
+      <c r="T27" s="54"/>
+      <c r="U27" s="55"/>
       <c r="V27" s="3"/>
       <c r="W27" s="3"/>
     </row>
@@ -3510,9 +3617,9 @@
         <f>+Q28/P28</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="S28" s="57"/>
-      <c r="T28" s="58"/>
-      <c r="U28" s="59"/>
+      <c r="S28" s="56"/>
+      <c r="T28" s="57"/>
+      <c r="U28" s="58"/>
       <c r="V28" s="3"/>
       <c r="W28" s="3"/>
     </row>
@@ -3708,10 +3815,12 @@
       <c r="P31" s="3">
         <v>4</v>
       </c>
-      <c r="Q31" s="3"/>
+      <c r="Q31" s="3">
+        <v>4</v>
+      </c>
       <c r="R31" s="6">
         <f>+Q31/P31</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S31" s="3" t="s">
         <v>60</v>
@@ -3735,32 +3844,56 @@
       <c r="D32" s="4">
         <v>46289</v>
       </c>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
-      <c r="G32" s="3"/>
+      <c r="E32" s="3">
+        <v>1</v>
+      </c>
+      <c r="F32" s="3">
+        <v>63</v>
+      </c>
+      <c r="G32" s="26">
+        <v>87782.97</v>
+      </c>
       <c r="H32" s="20">
         <f>+J32+L32+N32</f>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="I32" s="23">
         <f>+K32+M32+O32</f>
-        <v>0</v>
-      </c>
-      <c r="J32" s="24"/>
-      <c r="K32" s="3"/>
-      <c r="L32" s="7"/>
-      <c r="M32" s="6"/>
-      <c r="N32" s="3"/>
+        <v>41975</v>
+      </c>
+      <c r="J32" s="24">
+        <v>19</v>
+      </c>
+      <c r="K32" s="26">
+        <v>37579.440000000002</v>
+      </c>
+      <c r="L32" s="7">
+        <v>3</v>
+      </c>
+      <c r="M32" s="25">
+        <v>4395.5600000000004</v>
+      </c>
+      <c r="N32" s="3">
+        <v>0</v>
+      </c>
       <c r="O32" s="3"/>
-      <c r="P32" s="3"/>
+      <c r="P32" s="3">
+        <v>4</v>
+      </c>
       <c r="Q32" s="3"/>
-      <c r="R32" s="6" t="e">
+      <c r="R32" s="6">
         <f>+Q32/P32</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S32" s="3"/>
-      <c r="T32" s="3"/>
-      <c r="U32" s="3"/>
+        <v>0</v>
+      </c>
+      <c r="S32" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="T32" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="U32" s="3" t="s">
+        <v>63</v>
+      </c>
       <c r="V32" s="3"/>
       <c r="W32" s="3"/>
     </row>
@@ -3793,7 +3926,7 @@
       <c r="M33" s="6"/>
       <c r="N33" s="3"/>
       <c r="O33" s="4"/>
-      <c r="P33" s="53"/>
+      <c r="P33" s="52"/>
       <c r="Q33" s="3"/>
       <c r="R33" s="6" t="e">
         <f>+Q33/P33</f>
@@ -3834,7 +3967,7 @@
       <c r="M34" s="6"/>
       <c r="N34" s="3"/>
       <c r="O34" s="4"/>
-      <c r="P34" s="53"/>
+      <c r="P34" s="52"/>
       <c r="Q34" s="3"/>
       <c r="R34" s="6" t="e">
         <f>+Q34/P34</f>
@@ -3875,7 +4008,7 @@
       <c r="M35" s="6"/>
       <c r="N35" s="3"/>
       <c r="O35" s="7"/>
-      <c r="P35" s="53"/>
+      <c r="P35" s="52"/>
       <c r="Q35" s="3"/>
       <c r="R35" s="6" t="e">
         <f>+Q35/P35</f>
@@ -3916,7 +4049,7 @@
       <c r="M36" s="6"/>
       <c r="N36" s="3"/>
       <c r="O36" s="7"/>
-      <c r="P36" s="53"/>
+      <c r="P36" s="52"/>
       <c r="Q36" s="3"/>
       <c r="R36" s="6" t="e">
         <f>+Q36/P36</f>
@@ -7801,7 +7934,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{832B4BB6-73A1-0947-9C41-1C84F7F76940}">
-  <dimension ref="B2:W130"/>
+  <dimension ref="B2:W131"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="4.5" customWidth="1"/>
@@ -7855,10 +7988,10 @@
         <v>7</v>
       </c>
       <c r="J2" s="12" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="K2" s="12" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="L2" s="12" t="s">
         <v>10</v>
@@ -8018,10 +8151,10 @@
         <v>#DIV/0!</v>
       </c>
       <c r="S4" s="3" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="T4" s="3" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="U4" s="3"/>
       <c r="V4" s="3"/>
@@ -8085,10 +8218,10 @@
         <v>1</v>
       </c>
       <c r="S5" s="3" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="T5" s="3" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="U5" s="3" t="s">
         <v>25</v>
@@ -8154,10 +8287,10 @@
         <v>1</v>
       </c>
       <c r="S6" s="3" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="T6" s="3" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="U6" s="3" t="s">
         <v>25</v>
@@ -8223,10 +8356,10 @@
         <v>1</v>
       </c>
       <c r="S7" s="3" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="T7" s="3" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="U7" s="3" t="s">
         <v>25</v>
@@ -8292,10 +8425,10 @@
         <v>#DIV/0!</v>
       </c>
       <c r="S8" s="14" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="T8" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="U8" s="3"/>
       <c r="V8" s="3"/>
@@ -8359,13 +8492,13 @@
         <v>#DIV/0!</v>
       </c>
       <c r="S9" s="14" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="T9" s="3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="U9" s="3" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="V9" s="3"/>
       <c r="W9" s="3"/>
@@ -8428,13 +8561,13 @@
         <v>1</v>
       </c>
       <c r="S10" s="14" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="T10" s="3" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="U10" s="3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="V10" s="3"/>
       <c r="W10" s="3"/>
@@ -8495,7 +8628,7 @@
         <v>0</v>
       </c>
       <c r="S11" s="13" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="T11" s="45"/>
       <c r="U11" s="3"/>
@@ -8560,13 +8693,13 @@
         <v>1</v>
       </c>
       <c r="S12" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="T12" s="3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="U12" s="3" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="V12" s="3"/>
       <c r="W12" s="3"/>
@@ -8755,10 +8888,10 @@
         <v>0</v>
       </c>
       <c r="S15" s="3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="T15" s="3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="U15" s="3"/>
       <c r="V15" s="3"/>
@@ -8822,13 +8955,13 @@
         <v>1</v>
       </c>
       <c r="S16" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="T16" s="3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="U16" s="3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
@@ -8891,10 +9024,10 @@
         <v>#DIV/0!</v>
       </c>
       <c r="S17" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="T17" s="3" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="U17" s="3"/>
       <c r="V17" s="3"/>
@@ -8932,13 +9065,13 @@
       <c r="J18" s="7">
         <v>1</v>
       </c>
-      <c r="K18" s="49">
+      <c r="K18" s="48">
         <v>1813.32</v>
       </c>
       <c r="L18" s="7">
         <v>2</v>
       </c>
-      <c r="M18" s="49">
+      <c r="M18" s="48">
         <v>9035.25</v>
       </c>
       <c r="N18" s="3">
@@ -8958,10 +9091,10 @@
         <v>1</v>
       </c>
       <c r="S18" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="T18" s="3" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="U18" s="3"/>
       <c r="V18" s="3"/>
@@ -8999,7 +9132,7 @@
       <c r="J19" s="7">
         <v>1</v>
       </c>
-      <c r="K19" s="49">
+      <c r="K19" s="48">
         <v>1813.32</v>
       </c>
       <c r="L19" s="3">
@@ -9025,13 +9158,13 @@
         <v>#DIV/0!</v>
       </c>
       <c r="S19" s="3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="T19" s="3" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="U19" s="3" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
@@ -9068,7 +9201,7 @@
       <c r="J20" s="7">
         <v>1</v>
       </c>
-      <c r="K20" s="49">
+      <c r="K20" s="48">
         <v>1813.32</v>
       </c>
       <c r="L20" s="3">
@@ -9094,13 +9227,13 @@
         <v>#DIV/0!</v>
       </c>
       <c r="S20" s="3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="T20" s="3" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="U20" s="3" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="V20" s="3"/>
       <c r="W20" s="3"/>
@@ -9137,7 +9270,7 @@
       <c r="J21" s="7">
         <v>2</v>
       </c>
-      <c r="K21" s="49">
+      <c r="K21" s="48">
         <v>5893</v>
       </c>
       <c r="L21" s="3">
@@ -9163,13 +9296,13 @@
         <v>#DIV/0!</v>
       </c>
       <c r="S21" s="3" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="T21" s="3" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="U21" s="3" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="V21" s="3"/>
       <c r="W21" s="3"/>
@@ -9206,7 +9339,7 @@
       <c r="J22" s="7">
         <v>2</v>
       </c>
-      <c r="K22" s="51">
+      <c r="K22" s="50">
         <v>5893</v>
       </c>
       <c r="L22" s="3">
@@ -9232,13 +9365,13 @@
         <v>1</v>
       </c>
       <c r="S22" s="3" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="T22" s="3" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="U22" s="3" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="V22" s="3"/>
       <c r="W22" s="3"/>
@@ -9275,7 +9408,7 @@
       <c r="J23" s="7">
         <v>3</v>
       </c>
-      <c r="K23" s="51">
+      <c r="K23" s="50">
         <v>8337.7000000000007</v>
       </c>
       <c r="L23" s="7">
@@ -9301,10 +9434,10 @@
         <v>0.5</v>
       </c>
       <c r="S23" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="T23" s="3" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="U23" s="3"/>
       <c r="V23" s="3"/>
@@ -9342,7 +9475,7 @@
       <c r="J24" s="7">
         <v>3</v>
       </c>
-      <c r="K24" s="51">
+      <c r="K24" s="50">
         <v>8337.7000000000007</v>
       </c>
       <c r="L24" s="7">
@@ -9354,7 +9487,7 @@
       <c r="N24" s="3">
         <v>1</v>
       </c>
-      <c r="O24" s="52">
+      <c r="O24" s="51">
         <v>7638.75</v>
       </c>
       <c r="P24" s="3">
@@ -9368,10 +9501,10 @@
         <v>1</v>
       </c>
       <c r="S24" s="3" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="T24" s="3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="U24" s="3"/>
       <c r="V24" s="3"/>
@@ -9409,7 +9542,7 @@
       <c r="J25" s="7">
         <v>3</v>
       </c>
-      <c r="K25" s="51">
+      <c r="K25" s="50">
         <v>8337.7000000000007</v>
       </c>
       <c r="L25" s="7">
@@ -9421,7 +9554,7 @@
       <c r="N25" s="3">
         <v>1</v>
       </c>
-      <c r="O25" s="52">
+      <c r="O25" s="51">
         <v>7638.75</v>
       </c>
       <c r="P25" s="3">
@@ -9435,10 +9568,10 @@
         <v>1</v>
       </c>
       <c r="S25" s="3" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="T25" s="3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="U25" s="3"/>
       <c r="V25" s="3"/>
@@ -9476,7 +9609,7 @@
       <c r="J26" s="7">
         <v>2</v>
       </c>
-      <c r="K26" s="51">
+      <c r="K26" s="50">
         <v>5893</v>
       </c>
       <c r="L26" s="7">
@@ -9488,7 +9621,7 @@
       <c r="N26" s="3">
         <v>2</v>
       </c>
-      <c r="O26" s="51">
+      <c r="O26" s="50">
         <v>14241.4</v>
       </c>
       <c r="P26" s="3">
@@ -9502,13 +9635,13 @@
         <v>1</v>
       </c>
       <c r="S26" s="3" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="T26" s="3" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="U26" s="3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="V26" s="3"/>
       <c r="W26" s="3"/>
@@ -9545,7 +9678,7 @@
       <c r="J27" s="7">
         <v>2</v>
       </c>
-      <c r="K27" s="51">
+      <c r="K27" s="50">
         <v>5893</v>
       </c>
       <c r="L27" s="7">
@@ -9557,7 +9690,7 @@
       <c r="N27" s="3">
         <v>2</v>
       </c>
-      <c r="O27" s="51">
+      <c r="O27" s="50">
         <v>14241.4</v>
       </c>
       <c r="P27" s="3">
@@ -9571,13 +9704,13 @@
         <v>1</v>
       </c>
       <c r="S27" s="3" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="T27" s="3" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="U27" s="3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="V27" s="3"/>
       <c r="W27" s="3"/>
@@ -9614,7 +9747,7 @@
       <c r="J28" s="7">
         <v>2</v>
       </c>
-      <c r="K28" s="51">
+      <c r="K28" s="50">
         <v>5893</v>
       </c>
       <c r="L28" s="7">
@@ -9626,7 +9759,7 @@
       <c r="N28" s="3">
         <v>2</v>
       </c>
-      <c r="O28" s="51">
+      <c r="O28" s="50">
         <v>14241.4</v>
       </c>
       <c r="P28" s="3">
@@ -9640,13 +9773,13 @@
         <v>1</v>
       </c>
       <c r="S28" s="3" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="T28" s="3" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="U28" s="3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="V28" s="3"/>
       <c r="W28" s="3"/>
@@ -9683,7 +9816,7 @@
       <c r="J29" s="7">
         <v>4</v>
       </c>
-      <c r="K29" s="51">
+      <c r="K29" s="50">
         <v>20134.400000000001</v>
       </c>
       <c r="L29" s="7">
@@ -9709,10 +9842,10 @@
         <v>1</v>
       </c>
       <c r="S29" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="T29" s="3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="U29" s="3"/>
       <c r="V29" s="3"/>
@@ -9750,7 +9883,7 @@
       <c r="J30" s="7">
         <v>5</v>
       </c>
-      <c r="K30" s="51">
+      <c r="K30" s="50">
         <v>27800.6</v>
       </c>
       <c r="L30" s="7">
@@ -9776,16 +9909,16 @@
         <v>1</v>
       </c>
       <c r="S30" s="3" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="T30" s="3" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="U30" s="3"/>
       <c r="V30" s="3"/>
       <c r="W30" s="3"/>
     </row>
-    <row r="31" spans="2:23">
+    <row r="31" spans="2:23" ht="15.75">
       <c r="B31" s="3" t="str">
         <f t="shared" si="0"/>
         <v>Sep</v>
@@ -9817,7 +9950,7 @@
       <c r="J31" s="7">
         <v>3</v>
       </c>
-      <c r="K31" s="3">
+      <c r="K31" s="50">
         <v>13559.45</v>
       </c>
       <c r="L31" s="7">
@@ -9843,18 +9976,18 @@
         <v>#DIV/0!</v>
       </c>
       <c r="S31" s="3" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="T31" s="3" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="U31" s="3" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="V31" s="3"/>
       <c r="W31" s="3"/>
     </row>
-    <row r="32" spans="2:23">
+    <row r="32" spans="2:23" ht="15.75">
       <c r="B32" s="3" t="str">
         <f t="shared" si="0"/>
         <v>Sep</v>
@@ -9866,36 +9999,64 @@
       <c r="D32" s="4">
         <v>46289</v>
       </c>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
-      <c r="G32" s="3"/>
+      <c r="E32" s="3">
+        <v>2</v>
+      </c>
+      <c r="F32" s="3">
+        <v>11</v>
+      </c>
+      <c r="G32" s="22">
+        <v>38512.699999999997</v>
+      </c>
       <c r="H32" s="20">
         <f>+J32+L32+N32</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I32" s="23">
         <f>+K32+M32+O32</f>
-        <v>0</v>
-      </c>
-      <c r="J32" s="6"/>
-      <c r="K32" s="3"/>
-      <c r="L32" s="7"/>
-      <c r="M32" s="6"/>
-      <c r="N32" s="3"/>
-      <c r="O32" s="7"/>
-      <c r="P32" s="3"/>
-      <c r="Q32" s="3"/>
+        <v>19299.150000000001</v>
+      </c>
+      <c r="J32" s="7">
+        <v>3</v>
+      </c>
+      <c r="K32" s="50">
+        <v>19299.150000000001</v>
+      </c>
+      <c r="L32" s="7">
+        <v>0</v>
+      </c>
+      <c r="M32" s="22">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="22">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>0</v>
+      </c>
       <c r="R32" s="21" t="e">
         <f>+Q32/P32</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="S32" s="3"/>
-      <c r="T32" s="3"/>
-      <c r="U32" s="3"/>
+      <c r="S32" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="T32" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="U32" s="3" t="s">
+        <v>107</v>
+      </c>
       <c r="V32" s="3"/>
       <c r="W32" s="3"/>
     </row>
-    <row r="33" spans="2:23">
+    <row r="33" spans="2:23" ht="15.75">
       <c r="B33" s="3" t="str">
         <f t="shared" si="0"/>
         <v>Sep</v>
@@ -9907,25 +10068,47 @@
       <c r="D33" s="4">
         <v>46290</v>
       </c>
-      <c r="E33" s="3"/>
-      <c r="F33" s="3"/>
-      <c r="G33" s="3"/>
+      <c r="E33" s="3">
+        <v>2</v>
+      </c>
+      <c r="F33" s="3">
+        <v>13</v>
+      </c>
+      <c r="G33" s="22">
+        <v>51037.4</v>
+      </c>
       <c r="H33" s="20">
         <f>+J33+L33+N33</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I33" s="23">
         <f>+K33+M33+O33</f>
-        <v>0</v>
-      </c>
-      <c r="J33" s="6"/>
-      <c r="K33" s="3"/>
-      <c r="L33" s="7"/>
-      <c r="M33" s="6"/>
-      <c r="N33" s="3"/>
-      <c r="O33" s="7"/>
-      <c r="P33" s="3"/>
-      <c r="Q33" s="3"/>
+        <v>6774.75</v>
+      </c>
+      <c r="J33" s="7">
+        <v>1</v>
+      </c>
+      <c r="K33" s="50">
+        <v>6774.75</v>
+      </c>
+      <c r="L33" s="7">
+        <v>0</v>
+      </c>
+      <c r="M33" s="22">
+        <v>0</v>
+      </c>
+      <c r="N33" s="3">
+        <v>0</v>
+      </c>
+      <c r="O33" s="22">
+        <v>0</v>
+      </c>
+      <c r="P33" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="3">
+        <v>0</v>
+      </c>
       <c r="R33" s="21" t="e">
         <f>+Q33/P33</f>
         <v>#DIV/0!</v>
@@ -9936,7 +10119,7 @@
       <c r="V33" s="3"/>
       <c r="W33" s="3"/>
     </row>
-    <row r="34" spans="2:23">
+    <row r="34" spans="2:23" ht="15.75">
       <c r="B34" s="3" t="str">
         <f t="shared" si="0"/>
         <v>Sep</v>
@@ -9960,7 +10143,7 @@
         <v>0</v>
       </c>
       <c r="J34" s="6"/>
-      <c r="K34" s="3"/>
+      <c r="K34" s="50"/>
       <c r="L34" s="7"/>
       <c r="M34" s="6"/>
       <c r="N34" s="3"/>
@@ -9977,7 +10160,7 @@
       <c r="V34" s="3"/>
       <c r="W34" s="3"/>
     </row>
-    <row r="35" spans="2:23">
+    <row r="35" spans="2:23" ht="15.75">
       <c r="B35" s="3" t="str">
         <f t="shared" si="0"/>
         <v>Sep</v>
@@ -10001,7 +10184,7 @@
         <v>0</v>
       </c>
       <c r="J35" s="6"/>
-      <c r="K35" s="3"/>
+      <c r="K35" s="50"/>
       <c r="L35" s="7"/>
       <c r="M35" s="6"/>
       <c r="N35" s="3"/>
@@ -10018,7 +10201,7 @@
       <c r="V35" s="3"/>
       <c r="W35" s="3"/>
     </row>
-    <row r="36" spans="2:23">
+    <row r="36" spans="2:23" ht="15.75">
       <c r="B36" s="3" t="str">
         <f t="shared" si="0"/>
         <v>Sep</v>
@@ -10042,7 +10225,7 @@
         <v>0</v>
       </c>
       <c r="J36" s="6"/>
-      <c r="K36" s="3"/>
+      <c r="K36" s="50"/>
       <c r="L36" s="7"/>
       <c r="M36" s="6"/>
       <c r="N36" s="3"/>
@@ -10059,7 +10242,7 @@
       <c r="V36" s="3"/>
       <c r="W36" s="3"/>
     </row>
-    <row r="37" spans="2:23">
+    <row r="37" spans="2:23" ht="15.75">
       <c r="B37" s="3" t="str">
         <f t="shared" si="0"/>
         <v>Sep</v>
@@ -10083,7 +10266,7 @@
         <v>0</v>
       </c>
       <c r="J37" s="6"/>
-      <c r="K37" s="3"/>
+      <c r="K37" s="50"/>
       <c r="L37" s="7"/>
       <c r="M37" s="6"/>
       <c r="N37" s="3"/>
@@ -10100,7 +10283,7 @@
       <c r="V37" s="3"/>
       <c r="W37" s="3"/>
     </row>
-    <row r="38" spans="2:23">
+    <row r="38" spans="2:23" ht="15.75">
       <c r="B38" s="3" t="str">
         <f t="shared" si="0"/>
         <v>Sep</v>
@@ -10124,7 +10307,7 @@
         <v>0</v>
       </c>
       <c r="J38" s="6"/>
-      <c r="K38" s="3"/>
+      <c r="K38" s="50"/>
       <c r="L38" s="7"/>
       <c r="M38" s="6"/>
       <c r="N38" s="3"/>
@@ -10141,7 +10324,7 @@
       <c r="V38" s="3"/>
       <c r="W38" s="3"/>
     </row>
-    <row r="39" spans="2:23">
+    <row r="39" spans="2:23" ht="15.75">
       <c r="B39" s="3" t="str">
         <f t="shared" si="0"/>
         <v>Oct</v>
@@ -10165,7 +10348,7 @@
         <v>0</v>
       </c>
       <c r="J39" s="6"/>
-      <c r="K39" s="3"/>
+      <c r="K39" s="50"/>
       <c r="L39" s="7"/>
       <c r="M39" s="6"/>
       <c r="N39" s="3"/>
@@ -10182,7 +10365,7 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
     </row>
-    <row r="40" spans="2:23">
+    <row r="40" spans="2:23" ht="15.75">
       <c r="B40" s="3" t="str">
         <f t="shared" si="0"/>
         <v>Oct</v>
@@ -10206,7 +10389,7 @@
         <v>0</v>
       </c>
       <c r="J40" s="6"/>
-      <c r="K40" s="3"/>
+      <c r="K40" s="50"/>
       <c r="L40" s="7"/>
       <c r="M40" s="6"/>
       <c r="N40" s="3"/>
@@ -10223,7 +10406,7 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
     </row>
-    <row r="41" spans="2:23">
+    <row r="41" spans="2:23" ht="15.75">
       <c r="B41" s="3" t="str">
         <f t="shared" si="0"/>
         <v>Oct</v>
@@ -10247,7 +10430,7 @@
         <v>0</v>
       </c>
       <c r="J41" s="6"/>
-      <c r="K41" s="3"/>
+      <c r="K41" s="50"/>
       <c r="L41" s="7"/>
       <c r="M41" s="6"/>
       <c r="N41" s="3"/>
@@ -10264,7 +10447,7 @@
       <c r="V41" s="3"/>
       <c r="W41" s="3"/>
     </row>
-    <row r="42" spans="2:23">
+    <row r="42" spans="2:23" ht="15.75">
       <c r="B42" s="3" t="str">
         <f t="shared" si="0"/>
         <v>Oct</v>
@@ -10288,7 +10471,7 @@
         <v>0</v>
       </c>
       <c r="J42" s="6"/>
-      <c r="K42" s="3"/>
+      <c r="K42" s="50"/>
       <c r="L42" s="7"/>
       <c r="M42" s="6"/>
       <c r="N42" s="3"/>
@@ -10305,7 +10488,7 @@
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
     </row>
-    <row r="43" spans="2:23">
+    <row r="43" spans="2:23" ht="15.75">
       <c r="B43" s="3" t="str">
         <f t="shared" si="0"/>
         <v>Oct</v>
@@ -10329,7 +10512,7 @@
         <v>0</v>
       </c>
       <c r="J43" s="6"/>
-      <c r="K43" s="3"/>
+      <c r="K43" s="50"/>
       <c r="L43" s="7"/>
       <c r="M43" s="6"/>
       <c r="N43" s="3"/>
@@ -10346,7 +10529,7 @@
       <c r="V43" s="3"/>
       <c r="W43" s="3"/>
     </row>
-    <row r="44" spans="2:23">
+    <row r="44" spans="2:23" ht="15.75">
       <c r="B44" s="3" t="str">
         <f t="shared" si="0"/>
         <v>Oct</v>
@@ -10370,7 +10553,7 @@
         <v>0</v>
       </c>
       <c r="J44" s="6"/>
-      <c r="K44" s="3"/>
+      <c r="K44" s="50"/>
       <c r="L44" s="7"/>
       <c r="M44" s="6"/>
       <c r="N44" s="3"/>
@@ -10387,7 +10570,7 @@
       <c r="V44" s="3"/>
       <c r="W44" s="3"/>
     </row>
-    <row r="45" spans="2:23">
+    <row r="45" spans="2:23" ht="15.75">
       <c r="B45" s="3" t="str">
         <f t="shared" si="0"/>
         <v>Oct</v>
@@ -10411,7 +10594,7 @@
         <v>0</v>
       </c>
       <c r="J45" s="6"/>
-      <c r="K45" s="3"/>
+      <c r="K45" s="50"/>
       <c r="L45" s="7"/>
       <c r="M45" s="6"/>
       <c r="N45" s="3"/>
@@ -10428,7 +10611,7 @@
       <c r="V45" s="3"/>
       <c r="W45" s="3"/>
     </row>
-    <row r="46" spans="2:23">
+    <row r="46" spans="2:23" ht="15.75">
       <c r="B46" s="3" t="str">
         <f t="shared" si="0"/>
         <v>Oct</v>
@@ -10452,7 +10635,7 @@
         <v>0</v>
       </c>
       <c r="J46" s="6"/>
-      <c r="K46" s="3"/>
+      <c r="K46" s="50"/>
       <c r="L46" s="7"/>
       <c r="M46" s="6"/>
       <c r="N46" s="3"/>
@@ -10469,7 +10652,7 @@
       <c r="V46" s="3"/>
       <c r="W46" s="3"/>
     </row>
-    <row r="47" spans="2:23">
+    <row r="47" spans="2:23" ht="15.75">
       <c r="B47" s="3" t="str">
         <f t="shared" si="0"/>
         <v>Oct</v>
@@ -10493,7 +10676,7 @@
         <v>0</v>
       </c>
       <c r="J47" s="6"/>
-      <c r="K47" s="3"/>
+      <c r="K47" s="50"/>
       <c r="L47" s="7"/>
       <c r="M47" s="6"/>
       <c r="N47" s="3"/>
@@ -10510,7 +10693,7 @@
       <c r="V47" s="3"/>
       <c r="W47" s="3"/>
     </row>
-    <row r="48" spans="2:23">
+    <row r="48" spans="2:23" ht="15.75">
       <c r="B48" s="3" t="str">
         <f t="shared" si="0"/>
         <v>Oct</v>
@@ -10534,7 +10717,7 @@
         <v>0</v>
       </c>
       <c r="J48" s="6"/>
-      <c r="K48" s="3"/>
+      <c r="K48" s="50"/>
       <c r="L48" s="7"/>
       <c r="M48" s="6"/>
       <c r="N48" s="3"/>
@@ -10551,7 +10734,7 @@
       <c r="V48" s="3"/>
       <c r="W48" s="3"/>
     </row>
-    <row r="49" spans="2:23">
+    <row r="49" spans="2:23" ht="15.75">
       <c r="B49" s="3" t="str">
         <f t="shared" si="0"/>
         <v>Oct</v>
@@ -10575,7 +10758,7 @@
         <v>0</v>
       </c>
       <c r="J49" s="6"/>
-      <c r="K49" s="3"/>
+      <c r="K49" s="50"/>
       <c r="L49" s="7"/>
       <c r="M49" s="6"/>
       <c r="N49" s="3"/>
@@ -10592,7 +10775,7 @@
       <c r="V49" s="3"/>
       <c r="W49" s="3"/>
     </row>
-    <row r="50" spans="2:23">
+    <row r="50" spans="2:23" ht="15.75">
       <c r="B50" s="3" t="str">
         <f t="shared" si="0"/>
         <v>Oct</v>
@@ -10616,7 +10799,7 @@
         <v>0</v>
       </c>
       <c r="J50" s="6"/>
-      <c r="K50" s="3"/>
+      <c r="K50" s="50"/>
       <c r="L50" s="7"/>
       <c r="M50" s="6"/>
       <c r="N50" s="3"/>
@@ -10633,7 +10816,7 @@
       <c r="V50" s="3"/>
       <c r="W50" s="3"/>
     </row>
-    <row r="51" spans="2:23">
+    <row r="51" spans="2:23" ht="15.75">
       <c r="B51" s="3" t="str">
         <f t="shared" si="0"/>
         <v>Oct</v>
@@ -10657,7 +10840,7 @@
         <v>0</v>
       </c>
       <c r="J51" s="6"/>
-      <c r="K51" s="3"/>
+      <c r="K51" s="50"/>
       <c r="L51" s="7"/>
       <c r="M51" s="6"/>
       <c r="N51" s="3"/>
@@ -10674,7 +10857,7 @@
       <c r="V51" s="3"/>
       <c r="W51" s="3"/>
     </row>
-    <row r="52" spans="2:23">
+    <row r="52" spans="2:23" ht="15.75">
       <c r="B52" s="3" t="str">
         <f t="shared" si="0"/>
         <v>Oct</v>
@@ -10698,7 +10881,7 @@
         <v>0</v>
       </c>
       <c r="J52" s="6"/>
-      <c r="K52" s="3"/>
+      <c r="K52" s="50"/>
       <c r="L52" s="7"/>
       <c r="M52" s="6"/>
       <c r="N52" s="3"/>
@@ -10715,7 +10898,7 @@
       <c r="V52" s="3"/>
       <c r="W52" s="3"/>
     </row>
-    <row r="53" spans="2:23">
+    <row r="53" spans="2:23" ht="15.75">
       <c r="B53" s="3" t="str">
         <f t="shared" si="0"/>
         <v>Oct</v>
@@ -10739,7 +10922,7 @@
         <v>0</v>
       </c>
       <c r="J53" s="6"/>
-      <c r="K53" s="3"/>
+      <c r="K53" s="50"/>
       <c r="L53" s="7"/>
       <c r="M53" s="6"/>
       <c r="N53" s="3"/>
@@ -13913,13 +14096,14 @@
       <c r="V130" s="3"/>
       <c r="W130" s="3"/>
     </row>
+    <row r="131" spans="2:23" ht="15.75"/>
   </sheetData>
   <conditionalFormatting sqref="N3:N130">
     <cfRule type="cellIs" dxfId="7" priority="7" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K31:K130">
+  <conditionalFormatting sqref="K54:K130">
     <cfRule type="cellIs" dxfId="6" priority="6" operator="lessThan">
       <formula>0</formula>
     </cfRule>
@@ -13977,40 +14161,40 @@
         <v>2</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
     </row>
     <row r="3" spans="2:16">
@@ -14114,7 +14298,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
     </row>
     <row r="5" spans="2:16">
@@ -14164,7 +14348,7 @@
         <v>1</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
     </row>
     <row r="6" spans="2:16">
@@ -14212,7 +14396,7 @@
         <v>1</v>
       </c>
       <c r="P6" s="3" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
     </row>
     <row r="7" spans="2:16">
@@ -14260,7 +14444,7 @@
         <v>1</v>
       </c>
       <c r="P7" s="3" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
     </row>
     <row r="8" spans="2:16">
@@ -14309,7 +14493,7 @@
         <v>1</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
     </row>
     <row r="9" spans="2:16">
@@ -14358,7 +14542,7 @@
         <v>1</v>
       </c>
       <c r="P9" s="3" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
     </row>
     <row r="10" spans="2:16">
@@ -14387,7 +14571,7 @@
         <v>5</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="J10" s="3">
         <v>0</v>
@@ -14407,7 +14591,7 @@
         <v>1</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
     </row>
     <row r="11" spans="2:16">
@@ -14456,7 +14640,7 @@
         <v>1</v>
       </c>
       <c r="P11" s="3" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
     </row>
     <row r="12" spans="2:16">
@@ -14506,7 +14690,7 @@
         <v>1</v>
       </c>
       <c r="P12" s="3" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
     </row>
     <row r="13" spans="2:16">
@@ -14556,7 +14740,7 @@
         <v>1</v>
       </c>
       <c r="P13" s="3" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14" spans="2:16">
@@ -14604,7 +14788,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="P14" s="3" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
     </row>
     <row r="15" spans="2:16">
@@ -14654,7 +14838,7 @@
         <v>1</v>
       </c>
       <c r="P15" s="3" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="16" spans="2:16">
@@ -14704,7 +14888,7 @@
         <v>1</v>
       </c>
       <c r="P16" s="3" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="17" spans="2:18">
@@ -14754,7 +14938,7 @@
         <v>1</v>
       </c>
       <c r="P17" s="3" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
     </row>
     <row r="18" spans="2:18">
@@ -14804,7 +14988,7 @@
         <v>1</v>
       </c>
       <c r="P18" s="3" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
     </row>
     <row r="19" spans="2:18">
@@ -14854,10 +15038,10 @@
         <v>1</v>
       </c>
       <c r="P19" s="3" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="R19" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
     </row>
     <row r="20" spans="2:18">
@@ -14907,7 +15091,7 @@
         <v>1</v>
       </c>
       <c r="P20" s="3" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
     </row>
     <row r="21" spans="2:18">
@@ -14957,7 +15141,7 @@
         <v>1</v>
       </c>
       <c r="P21" s="3" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
     </row>
     <row r="22" spans="2:18">
@@ -15007,7 +15191,7 @@
         <v>1</v>
       </c>
       <c r="P22" s="3" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
     </row>
     <row r="23" spans="2:18" ht="15.75">
@@ -15057,7 +15241,7 @@
         <v>1</v>
       </c>
       <c r="P23" s="3" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
     </row>
     <row r="24" spans="2:18" ht="15.75">
@@ -15107,7 +15291,7 @@
         <v>1</v>
       </c>
       <c r="P24" s="3" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
     </row>
     <row r="25" spans="2:18">
@@ -15157,7 +15341,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="P25" s="3" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
     </row>
     <row r="26" spans="2:18">
@@ -15207,7 +15391,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="P26" s="3" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="27" spans="2:18">
@@ -15257,7 +15441,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="P27" s="3" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="28" spans="2:18">
@@ -15307,7 +15491,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="P28" s="3" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="29" spans="2:18">
@@ -15357,7 +15541,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="P29" s="3" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
     </row>
     <row r="30" spans="2:18">
@@ -15407,7 +15591,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="P30" s="3" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
     </row>
     <row r="31" spans="2:18">
@@ -15457,7 +15641,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="P31" s="3" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
     </row>
     <row r="32" spans="2:18">
@@ -15472,27 +15656,43 @@
       <c r="D32" s="4">
         <v>46289</v>
       </c>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
-      <c r="G32" s="21" t="e">
+      <c r="E32" s="3">
+        <v>952</v>
+      </c>
+      <c r="F32" s="3">
+        <v>953</v>
+      </c>
+      <c r="G32" s="21">
         <f>+(F32-E32)/E32</f>
-        <v>#DIV/0!</v>
+        <v>1.0504201680672268E-3</v>
       </c>
       <c r="H32" s="20">
         <f>+E32-F32</f>
-        <v>0</v>
-      </c>
-      <c r="I32" s="7"/>
-      <c r="J32" s="3"/>
-      <c r="K32" s="3"/>
-      <c r="L32" s="3"/>
-      <c r="M32" s="3"/>
+        <v>-1</v>
+      </c>
+      <c r="I32" s="7">
+        <v>216081.28</v>
+      </c>
+      <c r="J32" s="3">
+        <v>1</v>
+      </c>
+      <c r="K32" s="3">
+        <v>1</v>
+      </c>
+      <c r="L32" s="3">
+        <v>380</v>
+      </c>
+      <c r="M32" s="3">
+        <v>0</v>
+      </c>
       <c r="N32" s="3"/>
       <c r="O32" s="21" t="e">
         <f>1-(N32/M32)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="P32" s="3"/>
+      <c r="P32" s="3" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="33" spans="2:16">
       <c r="B33" s="3" t="str">
@@ -18863,16 +19063,16 @@
         <v>2</v>
       </c>
       <c r="E3" s="17" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="F3" s="17" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="G3" s="17" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="H3" s="17" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="I3" s="17" t="s">
         <v>17</v>
@@ -18915,16 +19115,16 @@
         <v>1</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="M4" s="5"/>
     </row>
@@ -18953,19 +19153,19 @@
         <v>3</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="L5" s="5" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="M5" s="5" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6" spans="2:13">
@@ -18993,16 +19193,16 @@
         <v>2</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="L6" s="5" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="M6" s="5"/>
     </row>
@@ -19029,13 +19229,13 @@
         <v>2</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="L7" s="5"/>
       <c r="M7" s="5"/>
@@ -19063,13 +19263,13 @@
         <v>2</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="L8" s="5"/>
       <c r="M8" s="5"/>
@@ -19099,13 +19299,13 @@
         <v>3</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="L9" s="5"/>
       <c r="M9" s="5"/>
@@ -19135,10 +19335,10 @@
         <v>2</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="K10" s="5"/>
       <c r="L10" s="5"/>
@@ -19169,10 +19369,10 @@
         <v>3</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="K11" s="5"/>
       <c r="L11" s="5"/>
@@ -19233,13 +19433,13 @@
         <v>3</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="K13" s="5" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="L13" s="5"/>
       <c r="M13" s="5"/>
@@ -19269,7 +19469,7 @@
         <v>2</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="J14" s="5"/>
       <c r="K14" s="5"/>
@@ -19301,10 +19501,10 @@
         <v>2</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="K15" s="5"/>
       <c r="L15" s="5"/>
@@ -19335,10 +19535,10 @@
         <v>2</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="K16" s="5"/>
       <c r="L16" s="5"/>
@@ -19369,10 +19569,10 @@
         <v>2</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="K17" s="5"/>
       <c r="L17" s="5"/>
@@ -19403,19 +19603,19 @@
         <v>2</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="K18" s="5" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="L18" s="5" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="M18" s="5" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
     </row>
     <row r="19" spans="2:13" ht="15.75">
@@ -19443,19 +19643,19 @@
         <v>1</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="J19" s="50" t="s">
-        <v>152</v>
+        <v>155</v>
+      </c>
+      <c r="J19" s="49" t="s">
+        <v>159</v>
       </c>
       <c r="K19" s="5" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="L19" s="5" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="M19" s="5" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
     </row>
     <row r="20" spans="2:13">
@@ -19483,19 +19683,19 @@
         <v>2</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="J20" s="5" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="K20" s="5" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="L20" s="5" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="M20" s="5" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
     </row>
     <row r="21" spans="2:13">
@@ -19523,19 +19723,19 @@
         <v>2</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="K21" s="5" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="L21" s="5" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="M21" s="5" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
     </row>
     <row r="22" spans="2:13">
@@ -19563,19 +19763,19 @@
         <v>2</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="J22" s="5" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="K22" s="5" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="L22" s="5" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="M22" s="5" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
     </row>
     <row r="23" spans="2:13">
@@ -19603,19 +19803,19 @@
         <v>2</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="K23" s="5" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="L23" s="5" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="M23" s="5" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
     </row>
     <row r="24" spans="2:13">
@@ -19643,19 +19843,19 @@
         <v>1</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="J24" s="5" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="K24" s="5" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="L24" s="5" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="M24" s="5" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
     </row>
     <row r="25" spans="2:13">
@@ -19683,13 +19883,13 @@
         <v>1</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="J25" s="5" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="K25" s="5" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="L25" s="5"/>
       <c r="M25" s="5"/>
@@ -19719,16 +19919,16 @@
         <v>1</v>
       </c>
       <c r="I26" s="5" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="J26" s="5" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="K26" s="5" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="L26" s="5" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="M26" s="5"/>
     </row>
@@ -19757,16 +19957,16 @@
         <v>1</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="J27" s="5" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="K27" s="5" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="L27" s="5" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="M27" s="5"/>
     </row>
@@ -19795,13 +19995,13 @@
         <v>1</v>
       </c>
       <c r="I28" s="5" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="J28" s="5" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="K28" s="5" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="L28" s="5"/>
       <c r="M28" s="5"/>
@@ -19831,13 +20031,13 @@
         <v>1</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="J29" s="5" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="K29" s="5" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="L29" s="5"/>
       <c r="M29" s="5"/>
@@ -19867,16 +20067,16 @@
         <v>1</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="J30" s="5" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="K30" s="5" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="L30" s="5" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="M30" s="5"/>
     </row>
@@ -19905,10 +20105,10 @@
         <v>1</v>
       </c>
       <c r="I31" s="5" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="J31" s="5" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="K31" s="5"/>
       <c r="L31" s="5"/>
@@ -19939,13 +20139,13 @@
         <v>2</v>
       </c>
       <c r="I32" s="5" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="J32" s="5" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="K32" s="5" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="L32" s="5"/>
       <c r="M32" s="5"/>
@@ -19962,13 +20162,27 @@
       <c r="D33" s="4">
         <v>46289</v>
       </c>
-      <c r="E33" s="18"/>
-      <c r="F33" s="18"/>
-      <c r="G33" s="18"/>
-      <c r="H33" s="18"/>
-      <c r="I33" s="5"/>
-      <c r="J33" s="5"/>
-      <c r="K33" s="5"/>
+      <c r="E33" s="18">
+        <v>10</v>
+      </c>
+      <c r="F33" s="18">
+        <v>1</v>
+      </c>
+      <c r="G33" s="18">
+        <v>0</v>
+      </c>
+      <c r="H33" s="18">
+        <v>1</v>
+      </c>
+      <c r="I33" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="J33" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="K33" s="5" t="s">
+        <v>181</v>
+      </c>
       <c r="L33" s="5"/>
       <c r="M33" s="5"/>
     </row>
@@ -22130,7 +22344,7 @@
     </row>
     <row r="1048576" spans="11:11">
       <c r="K1048576" s="5" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
     </row>
   </sheetData>
@@ -22141,11 +22355,12 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6052D5D0-28BE-41ED-8C32-52AF0B1B7B94}">
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.75" customWidth="1"/>
     <col min="5" max="5" width="37.5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16.625" bestFit="1" customWidth="1"/>
@@ -22157,179 +22372,423 @@
     <col min="12" max="12" width="7.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:11">
       <c r="A1" s="37"/>
       <c r="B1" s="37"/>
-      <c r="C1" s="48" t="s">
-        <v>172</v>
-      </c>
-      <c r="D1" s="48" t="s">
-        <v>173</v>
-      </c>
-      <c r="E1" s="48" t="s">
-        <v>174</v>
-      </c>
-      <c r="F1" s="48" t="s">
-        <v>175</v>
-      </c>
-      <c r="G1" s="48" t="s">
-        <v>176</v>
-      </c>
-      <c r="H1" s="48" t="s">
-        <v>177</v>
-      </c>
-      <c r="I1" s="48" t="s">
-        <v>178</v>
-      </c>
-      <c r="J1" s="48" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="B2" t="s">
-        <v>180</v>
-      </c>
-      <c r="C2" s="48" t="s">
-        <v>181</v>
-      </c>
-      <c r="D2" s="48" t="s">
+      <c r="C1" s="60" t="s">
         <v>182</v>
       </c>
-      <c r="E2" s="48" t="s">
+      <c r="D1" s="60" t="s">
         <v>183</v>
       </c>
-      <c r="F2" s="48" t="s">
+      <c r="E1" s="60" t="s">
         <v>184</v>
       </c>
-      <c r="G2" s="48" t="s">
+      <c r="F1" s="60" t="s">
         <v>185</v>
       </c>
-      <c r="H2" s="48" t="s">
+      <c r="G1" s="60" t="s">
         <v>186</v>
       </c>
-      <c r="I2" s="48" t="s">
+      <c r="H1" s="60" t="s">
         <v>187</v>
       </c>
-      <c r="J2" s="48" t="s">
+      <c r="I1" s="60" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="47">
+      <c r="J1" s="60" t="s">
+        <v>189</v>
+      </c>
+      <c r="K1" s="66" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="61"/>
+      <c r="B2" s="61" t="s">
+        <v>191</v>
+      </c>
+      <c r="C2" s="47" t="s">
+        <v>192</v>
+      </c>
+      <c r="D2" s="47" t="s">
+        <v>193</v>
+      </c>
+      <c r="E2" s="47" t="s">
+        <v>194</v>
+      </c>
+      <c r="F2" s="47" t="s">
+        <v>195</v>
+      </c>
+      <c r="G2" s="47" t="s">
+        <v>196</v>
+      </c>
+      <c r="H2" s="47" t="s">
+        <v>197</v>
+      </c>
+      <c r="I2" s="47" t="s">
+        <v>198</v>
+      </c>
+      <c r="J2" s="47" t="s">
+        <v>199</v>
+      </c>
+      <c r="K2" s="67" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="62" t="s">
+        <v>201</v>
+      </c>
+      <c r="B3" s="63">
+        <f>SUM(C3:J3)</f>
+        <v>199934.86</v>
+      </c>
+      <c r="C3" s="65">
+        <v>158216.85999999999</v>
+      </c>
+      <c r="D3" s="65">
+        <v>33384.699999999997</v>
+      </c>
+      <c r="E3" s="65">
+        <v>600.5</v>
+      </c>
+      <c r="F3" s="65">
+        <v>3467.6</v>
+      </c>
+      <c r="G3" s="65">
+        <v>0</v>
+      </c>
+      <c r="H3" s="65">
+        <v>0</v>
+      </c>
+      <c r="I3" s="65">
+        <v>2349.15</v>
+      </c>
+      <c r="J3" s="65">
+        <v>1916.05</v>
+      </c>
+      <c r="K3" s="65"/>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="62">
+        <v>46265</v>
+      </c>
+      <c r="B4" s="63">
+        <f>SUM(C4:J4)</f>
+        <v>32085.96</v>
+      </c>
+      <c r="C4" s="65">
+        <v>24289.66</v>
+      </c>
+      <c r="D4" s="65">
+        <v>3522.8</v>
+      </c>
+      <c r="E4" s="65">
+        <v>148.19</v>
+      </c>
+      <c r="F4" s="65">
+        <v>1930.63</v>
+      </c>
+      <c r="G4" s="65">
+        <v>230</v>
+      </c>
+      <c r="H4" s="65">
+        <v>0</v>
+      </c>
+      <c r="I4" s="65">
+        <v>1531.66</v>
+      </c>
+      <c r="J4" s="65">
+        <v>433.02</v>
+      </c>
+      <c r="K4" s="65"/>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="62">
         <v>46272</v>
       </c>
-      <c r="B3">
-        <f>SUM(C3:J3)</f>
-        <v>22190.880000000005</v>
-      </c>
-      <c r="C3" s="48">
-        <v>8838.19</v>
-      </c>
-      <c r="D3" s="48">
-        <v>3522.8</v>
-      </c>
-      <c r="E3" s="48">
-        <v>148.19</v>
-      </c>
-      <c r="F3" s="48">
-        <v>3312.13</v>
-      </c>
-      <c r="G3" s="48">
-        <v>230</v>
-      </c>
-      <c r="H3" s="48">
-        <v>4562.42</v>
-      </c>
-      <c r="I3" s="48">
-        <v>1144.1300000000001</v>
-      </c>
-      <c r="J3" s="48">
-        <v>433.02</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="47">
-        <f>A3+7</f>
+      <c r="B5" s="63">
+        <f>SUM(C5:J5)</f>
+        <v>43276.490000000005</v>
+      </c>
+      <c r="C5" s="59">
+        <v>40836.76</v>
+      </c>
+      <c r="D5" s="59">
+        <v>0</v>
+      </c>
+      <c r="E5" s="59">
+        <v>76.900000000000006</v>
+      </c>
+      <c r="F5" s="59">
+        <v>1482.83</v>
+      </c>
+      <c r="G5" s="59">
+        <v>0</v>
+      </c>
+      <c r="H5" s="59">
+        <v>880</v>
+      </c>
+      <c r="I5" s="59"/>
+      <c r="J5" s="59"/>
+      <c r="K5" s="65"/>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" s="62">
+        <f>A5+7</f>
         <v>46279</v>
       </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="47">
-        <f t="shared" ref="A5:A17" si="0">A4+7</f>
+      <c r="B6" s="63">
+        <f>SUM(C6:J6)</f>
+        <v>23768.58</v>
+      </c>
+      <c r="C6" s="59">
+        <v>22968.080000000002</v>
+      </c>
+      <c r="D6" s="59">
+        <v>0</v>
+      </c>
+      <c r="E6" s="59">
+        <v>0</v>
+      </c>
+      <c r="F6" s="59">
+        <v>800.5</v>
+      </c>
+      <c r="G6" s="59">
+        <v>0</v>
+      </c>
+      <c r="H6" s="59">
+        <v>0</v>
+      </c>
+      <c r="I6" s="59">
+        <v>0</v>
+      </c>
+      <c r="J6" s="59">
+        <v>0</v>
+      </c>
+      <c r="K6" s="65"/>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" s="62">
+        <f t="shared" ref="A7:A19" si="0">A6+7</f>
         <v>46286</v>
       </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="47">
+      <c r="B7" s="63">
+        <f>SUM(C7:K7)</f>
+        <v>57337.939999999995</v>
+      </c>
+      <c r="C7" s="65">
+        <v>53313.54</v>
+      </c>
+      <c r="D7" s="65"/>
+      <c r="E7" s="65"/>
+      <c r="F7" s="65">
+        <v>3236.99</v>
+      </c>
+      <c r="G7" s="65">
+        <v>67.5</v>
+      </c>
+      <c r="H7" s="65"/>
+      <c r="I7" s="65">
+        <v>488.7</v>
+      </c>
+      <c r="J7" s="65"/>
+      <c r="K7" s="65">
+        <v>231.21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" s="62">
         <f t="shared" si="0"/>
         <v>46293</v>
       </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="47">
+      <c r="B8" s="64"/>
+      <c r="C8" s="61"/>
+      <c r="D8" s="61"/>
+      <c r="E8" s="61"/>
+      <c r="F8" s="61"/>
+      <c r="G8" s="61"/>
+      <c r="H8" s="61"/>
+      <c r="I8" s="61"/>
+      <c r="J8" s="61"/>
+      <c r="K8" s="61"/>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" s="62">
         <f t="shared" si="0"/>
         <v>46300</v>
       </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" s="47">
+      <c r="B9" s="64"/>
+      <c r="C9" s="61"/>
+      <c r="D9" s="61"/>
+      <c r="E9" s="61"/>
+      <c r="F9" s="61"/>
+      <c r="G9" s="61"/>
+      <c r="H9" s="61"/>
+      <c r="I9" s="61"/>
+      <c r="J9" s="61"/>
+      <c r="K9" s="61"/>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" s="62">
         <f t="shared" si="0"/>
         <v>46307</v>
       </c>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" s="47">
+      <c r="B10" s="64"/>
+      <c r="C10" s="61"/>
+      <c r="D10" s="61"/>
+      <c r="E10" s="61"/>
+      <c r="F10" s="61"/>
+      <c r="G10" s="61"/>
+      <c r="H10" s="61"/>
+      <c r="I10" s="61"/>
+      <c r="J10" s="61"/>
+      <c r="K10" s="61"/>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" s="62">
         <f t="shared" si="0"/>
         <v>46314</v>
       </c>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="47">
+      <c r="B11" s="64"/>
+      <c r="C11" s="61"/>
+      <c r="D11" s="61"/>
+      <c r="E11" s="61"/>
+      <c r="F11" s="61"/>
+      <c r="G11" s="61"/>
+      <c r="H11" s="61"/>
+      <c r="I11" s="61"/>
+      <c r="J11" s="61"/>
+      <c r="K11" s="61"/>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" s="62">
         <f t="shared" si="0"/>
         <v>46321</v>
       </c>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" s="47">
+      <c r="B12" s="64"/>
+      <c r="C12" s="61"/>
+      <c r="D12" s="61"/>
+      <c r="E12" s="61"/>
+      <c r="F12" s="61"/>
+      <c r="G12" s="61"/>
+      <c r="H12" s="61"/>
+      <c r="I12" s="61"/>
+      <c r="J12" s="61"/>
+      <c r="K12" s="61"/>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" s="62">
         <f t="shared" si="0"/>
         <v>46328</v>
       </c>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" s="47">
+      <c r="B13" s="64"/>
+      <c r="C13" s="61"/>
+      <c r="D13" s="61"/>
+      <c r="E13" s="61"/>
+      <c r="F13" s="61"/>
+      <c r="G13" s="61"/>
+      <c r="H13" s="61"/>
+      <c r="I13" s="61"/>
+      <c r="J13" s="61"/>
+      <c r="K13" s="61"/>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" s="62">
         <f t="shared" si="0"/>
         <v>46335</v>
       </c>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13" s="47">
+      <c r="B14" s="64"/>
+      <c r="C14" s="61"/>
+      <c r="D14" s="61"/>
+      <c r="E14" s="61"/>
+      <c r="F14" s="61"/>
+      <c r="G14" s="61"/>
+      <c r="H14" s="61"/>
+      <c r="I14" s="61"/>
+      <c r="J14" s="61"/>
+      <c r="K14" s="61"/>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" s="62">
         <f t="shared" si="0"/>
         <v>46342</v>
       </c>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14" s="47">
+      <c r="B15" s="64"/>
+      <c r="C15" s="61"/>
+      <c r="D15" s="61"/>
+      <c r="E15" s="61"/>
+      <c r="F15" s="61"/>
+      <c r="G15" s="61"/>
+      <c r="H15" s="61"/>
+      <c r="I15" s="61"/>
+      <c r="J15" s="61"/>
+      <c r="K15" s="61"/>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" s="62">
         <f t="shared" si="0"/>
         <v>46349</v>
       </c>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="A15" s="47">
+      <c r="B16" s="64"/>
+      <c r="C16" s="61"/>
+      <c r="D16" s="61"/>
+      <c r="E16" s="61"/>
+      <c r="F16" s="61"/>
+      <c r="G16" s="61"/>
+      <c r="H16" s="61"/>
+      <c r="I16" s="61"/>
+      <c r="J16" s="61"/>
+      <c r="K16" s="61"/>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" s="62">
         <f t="shared" si="0"/>
         <v>46356</v>
       </c>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="A16" s="47">
+      <c r="B17" s="64"/>
+      <c r="C17" s="61"/>
+      <c r="D17" s="61"/>
+      <c r="E17" s="61"/>
+      <c r="F17" s="61"/>
+      <c r="G17" s="61"/>
+      <c r="H17" s="61"/>
+      <c r="I17" s="61"/>
+      <c r="J17" s="61"/>
+      <c r="K17" s="61"/>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" s="62">
         <f t="shared" si="0"/>
         <v>46363</v>
       </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" s="47">
+      <c r="B18" s="64"/>
+      <c r="C18" s="61"/>
+      <c r="D18" s="61"/>
+      <c r="E18" s="61"/>
+      <c r="F18" s="61"/>
+      <c r="G18" s="61"/>
+      <c r="H18" s="61"/>
+      <c r="I18" s="61"/>
+      <c r="J18" s="61"/>
+      <c r="K18" s="61"/>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" s="62">
         <f t="shared" si="0"/>
         <v>46370</v>
       </c>
+      <c r="B19" s="64"/>
+      <c r="C19" s="61"/>
+      <c r="D19" s="61"/>
+      <c r="E19" s="61"/>
+      <c r="F19" s="61"/>
+      <c r="G19" s="61"/>
+      <c r="H19" s="61"/>
+      <c r="I19" s="61"/>
+      <c r="J19" s="61"/>
+      <c r="K19" s="61"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
